--- a/templates/[대국지아이에스]기초번호판설치점검_주간보고_템플릿.xlsx
+++ b/templates/[대국지아이에스]기초번호판설치점검_주간보고_템플릿.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSM\Downloads\public-보고서\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSM\Downloads\public-보고서\깃의 템플릿\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0345DE-ED7C-41C5-BEA1-C22C2770352E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="주간보고내용" sheetId="1" r:id="rId1"/>
@@ -414,51 +414,51 @@
     <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -731,220 +731,215 @@
   <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" style="9" customWidth="1"/>
-    <col min="2" max="6" width="22" style="9" customWidth="1"/>
-    <col min="7" max="16384" width="8.7109375" style="9"/>
+    <col min="1" max="1" width="14" style="4" customWidth="1"/>
+    <col min="2" max="6" width="22" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.7109375" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
     </row>
     <row r="9" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
     </row>
     <row r="15" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
     </row>
     <row r="21" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F24"/>
     <mergeCell ref="B6:F6"/>
@@ -952,6 +947,11 @@
     <mergeCell ref="A9:F12"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A15:F18"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -964,39 +964,39 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" style="9" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="20" style="9" customWidth="1"/>
-    <col min="4" max="5" width="14" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.7109375" style="9"/>
+    <col min="1" max="1" width="5" style="4" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="20" style="4" customWidth="1"/>
+    <col min="4" max="5" width="14" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="8.7109375" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1016,16 +1016,16 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="8">
         <v>405</v>
       </c>
       <c r="E5" s="2">
@@ -1033,16 +1033,16 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="17">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="11">
         <v>2397</v>
       </c>
       <c r="E6" s="2">
@@ -1050,16 +1050,16 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="8">
         <v>1015</v>
       </c>
       <c r="E7" s="2">
@@ -1067,16 +1067,16 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="17">
+      <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="11">
         <v>1104</v>
       </c>
       <c r="E8" s="2">
@@ -1084,16 +1084,16 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
+      <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="8">
         <v>1443</v>
       </c>
       <c r="E9" s="2">
@@ -1101,16 +1101,16 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="17">
+      <c r="A10" s="9">
         <v>6</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="11">
         <v>782</v>
       </c>
       <c r="E10" s="2">
@@ -1118,16 +1118,16 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="14">
+      <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="8">
         <v>974</v>
       </c>
       <c r="E11" s="2">
@@ -1135,16 +1135,16 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="A12" s="9">
         <v>8</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="11">
         <v>787</v>
       </c>
       <c r="E12" s="2">
@@ -1152,16 +1152,16 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="14">
+      <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="8">
         <v>312</v>
       </c>
       <c r="E13" s="2">
@@ -1169,16 +1169,16 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
+      <c r="A14" s="9">
         <v>10</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="11">
         <v>392</v>
       </c>
       <c r="E14" s="2">
@@ -1186,16 +1186,16 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
+      <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="8">
         <v>43</v>
       </c>
       <c r="E15" s="2">
@@ -1203,16 +1203,16 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="17">
+      <c r="A16" s="9">
         <v>12</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="11">
         <v>76</v>
       </c>
       <c r="E16" s="2">
@@ -1220,16 +1220,16 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="14">
+      <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="8">
         <v>208</v>
       </c>
       <c r="E17" s="2">
@@ -1237,16 +1237,16 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="17">
+      <c r="A18" s="9">
         <v>14</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="11">
         <v>968</v>
       </c>
       <c r="E18" s="2">
@@ -1254,16 +1254,16 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="14">
+      <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="8">
         <v>589</v>
       </c>
       <c r="E19" s="2">
@@ -1271,16 +1271,16 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="17">
+      <c r="A20" s="9">
         <v>16</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="11">
         <v>2124</v>
       </c>
       <c r="E20" s="2">
@@ -1288,16 +1288,16 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="14">
+      <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="8">
         <v>865</v>
       </c>
       <c r="E21" s="2">
@@ -1305,16 +1305,16 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="17">
+      <c r="A22" s="9">
         <v>18</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="11">
         <v>814</v>
       </c>
       <c r="E22" s="2">
@@ -1322,16 +1322,16 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="14">
+      <c r="A23" s="6">
         <v>19</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="8">
         <v>471</v>
       </c>
       <c r="E23" s="2">
@@ -1339,16 +1339,16 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="17">
+      <c r="A24" s="9">
         <v>20</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="11">
         <v>2328</v>
       </c>
       <c r="E24" s="2">
@@ -1356,16 +1356,16 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="14">
+      <c r="A25" s="6">
         <v>21</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="8">
         <v>976</v>
       </c>
       <c r="E25" s="2">
@@ -1373,16 +1373,16 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="17">
+      <c r="A26" s="9">
         <v>22</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="11">
         <v>398</v>
       </c>
       <c r="E26" s="2">
@@ -1390,16 +1390,16 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="14">
+      <c r="A27" s="6">
         <v>23</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="8">
         <v>60</v>
       </c>
       <c r="E27" s="2">
@@ -1407,16 +1407,16 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="17">
+      <c r="A28" s="9">
         <v>24</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="11">
         <v>2007</v>
       </c>
       <c r="E28" s="2">
